--- a/0001_ROBOS/CAPTAÇÃO/FORMS CIRURGIOES/Forms_Cirurgioes.xlsx
+++ b/0001_ROBOS/CAPTAÇÃO/FORMS CIRURGIOES/Forms_Cirurgioes.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y82"/>
+  <dimension ref="A1:Y87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7474,6 +7474,475 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>46184.64444444444</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>CAMILA PATRÍCIA DA SILVA BENTO</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>096737478</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>38904726808</v>
+      </c>
+      <c r="N83" t="n">
+        <v>35</v>
+      </c>
+      <c r="O83" t="n">
+        <v>11984268949</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q83" t="b">
+        <v>1</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>enviado para captação</t>
+        </is>
+      </c>
+      <c r="T83" t="n">
+        <v>380</v>
+      </c>
+      <c r="U83" s="1" t="n">
+        <v>33345</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>17/04/1991</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>46184.64513888889</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>ERIKA MARIA DA SILVA</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>094418641</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="n">
+        <v>33670620818</v>
+      </c>
+      <c r="N84" t="n">
+        <v>41</v>
+      </c>
+      <c r="O84" t="n">
+        <v>11980812325</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q84" t="b">
+        <v>1</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>enviado para captação</t>
+        </is>
+      </c>
+      <c r="T84" t="n">
+        <v>500</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18/04/1985  </t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>18/04/1985</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>46184.64652777778</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>LUANA DE MENDONÇA FURTADO CUNHA</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>092857092</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="n">
+        <v>35420859874</v>
+      </c>
+      <c r="N85" t="n">
+        <v>37</v>
+      </c>
+      <c r="O85" t="n">
+        <v>11912260375</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q85" t="b">
+        <v>1</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>enviado para captação</t>
+        </is>
+      </c>
+      <c r="T85" t="n">
+        <v>400</v>
+      </c>
+      <c r="U85" s="1" t="n">
+        <v>32317</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>23/06/1988</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1213</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>46184.64652777778</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>MARIA LUCIA PEREIRA PORTO DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>097420124</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="n">
+        <v>14890766898</v>
+      </c>
+      <c r="N86" t="n">
+        <v>60</v>
+      </c>
+      <c r="O86" t="n">
+        <v>11959427354</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q86" t="b">
+        <v>1</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>enviado para captação</t>
+        </is>
+      </c>
+      <c r="T86" t="n">
+        <v>380</v>
+      </c>
+      <c r="U86" s="1" t="n">
+        <v>24136</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>29/01/1966</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>46185.67916666667</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>RICHARD DA SILVA VILAPIANO</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>079649693</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>36441637820</v>
+      </c>
+      <c r="N87" t="n">
+        <v>37</v>
+      </c>
+      <c r="O87" t="n">
+        <v>11967904790</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Dom Pedro</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>enviado para captação</t>
+        </is>
+      </c>
+      <c r="T87" t="n">
+        <v>450</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/11/1988  </t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>11/11/1988</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0001_ROBOS/CAPTAÇÃO/FORMS CIRURGIOES/Forms_Cirurgioes.xlsx
+++ b/0001_ROBOS/CAPTAÇÃO/FORMS CIRURGIOES/Forms_Cirurgioes.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y87"/>
+  <dimension ref="A1:Y100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7943,6 +7943,1115 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>46188.74027777778</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Equipe - FERNANDO DE BARROS</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viviane Azevedo de oliveira </t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>095919032</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>8895412729</v>
+      </c>
+      <c r="N88" t="n">
+        <v>45</v>
+      </c>
+      <c r="O88" t="n">
+        <v>21964678072</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="Q88" t="b">
+        <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="n">
+        <v>60</v>
+      </c>
+      <c r="U88" s="1" t="n">
+        <v>29753</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>16/06/1981</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Equipe - FERNANDO DE BARROS</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>46189.7</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Luiz Alfredo</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonardo cesar dos santos pacheco </t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>094340036</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="n">
+        <v>14007861773</v>
+      </c>
+      <c r="N89" t="n">
+        <v>36</v>
+      </c>
+      <c r="O89" t="n">
+        <v>21990345044</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q89" t="b">
+        <v>0</v>
+      </c>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="n">
+        <v>60</v>
+      </c>
+      <c r="U89" s="1" t="n">
+        <v>24594</v>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>02/05/1967</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Luiz Alfredo</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>46189.70347222222</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Equipe - Instituto Castro</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Juliana Ferreira Junqueira Guerra</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>088988201</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>5548611607</v>
+      </c>
+      <c r="N90" t="n">
+        <v>45</v>
+      </c>
+      <c r="O90" t="n">
+        <v>11980887272</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q90" t="b">
+        <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="n">
+        <v>120</v>
+      </c>
+      <c r="U90" s="1" t="n">
+        <v>21328</v>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>23/05/1958</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Equipe - Instituto Castro</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>46190.53888888889</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Equipe - Instituto Castro</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Alessandra da Silva Rodrigues</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>087915475</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>29350990873</v>
+      </c>
+      <c r="N91" t="n">
+        <v>45</v>
+      </c>
+      <c r="O91" t="n">
+        <v>11967892248</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q91" t="b">
+        <v>0</v>
+      </c>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="n">
+        <v>380</v>
+      </c>
+      <c r="U91" s="1" t="n">
+        <v>29496</v>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>02/10/1980</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Equipe - Instituto Castro</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>46190.66319444445</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Equipe - FERNANDO DE BARROS</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Ana Flavia de Moraes Miguel</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>097507264</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="n">
+        <v>19961926714</v>
+      </c>
+      <c r="N92" t="n">
+        <v>26</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>(21)97552-7140</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="Q92" t="b">
+        <v>0</v>
+      </c>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="n">
+        <v>380</v>
+      </c>
+      <c r="U92" s="1" t="n">
+        <v>36574</v>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>18/02/2000</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Equipe - FERNANDO DE BARROS</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>46191.43958333333</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Equipe - FERNANDO DE BARROS</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Roberta Cavalheiro São Sabbas</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>097466941</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="n">
+        <v>12550149700</v>
+      </c>
+      <c r="N93" t="n">
+        <v>36</v>
+      </c>
+      <c r="O93" t="n">
+        <v>21993640944</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q93" t="b">
+        <v>0</v>
+      </c>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="n">
+        <v>75</v>
+      </c>
+      <c r="U93" s="1" t="n">
+        <v>32825</v>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>13/11/1989</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Equipe - FERNANDO DE BARROS</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>46192.37638888889</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>KETHLLEN LOPES FRANÇA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>082020177</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="n">
+        <v>18849916701</v>
+      </c>
+      <c r="N94" t="n">
+        <v>25</v>
+      </c>
+      <c r="O94" t="n">
+        <v>21966942319</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q94" t="b">
+        <v>0</v>
+      </c>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="n">
+        <v>380</v>
+      </c>
+      <c r="U94" s="1" t="n">
+        <v>36926</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>04/02/2001</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>46192.39722222222</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>WERONICA SILVA SOARES</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>095796652</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="n">
+        <v>5322498796</v>
+      </c>
+      <c r="N95" t="n">
+        <v>45</v>
+      </c>
+      <c r="O95" t="n">
+        <v>21966254990</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q95" t="b">
+        <v>0</v>
+      </c>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="n">
+        <v>380</v>
+      </c>
+      <c r="U95" s="1" t="n">
+        <v>29533</v>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>08/11/1980</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>46192.50069444445</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>SUELEN DE CARVALHO DIAS SOUSA SOARES</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>082599167</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="n">
+        <v>13245574789</v>
+      </c>
+      <c r="N96" t="n">
+        <v>38</v>
+      </c>
+      <c r="O96" t="n">
+        <v>21998162777</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q96" t="b">
+        <v>0</v>
+      </c>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="n">
+        <v>380</v>
+      </c>
+      <c r="U96" s="1" t="n">
+        <v>32242</v>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>09/04/1988</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1226</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>46195.41944444444</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>LUCAS SILVA ALVES</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>088397127</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="n">
+        <v>51200118880</v>
+      </c>
+      <c r="N97" t="n">
+        <v>23</v>
+      </c>
+      <c r="O97" t="n">
+        <v>11989775184</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q97" t="b">
+        <v>0</v>
+      </c>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="n">
+        <v>380</v>
+      </c>
+      <c r="U97" s="1" t="n">
+        <v>37527</v>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>28/09/2002</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>46195.42569444444</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>DENISE DOS SANTOS FERREIRA</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>074162184</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="n">
+        <v>39422138850</v>
+      </c>
+      <c r="N98" t="n">
+        <v>33</v>
+      </c>
+      <c r="O98" t="n">
+        <v>11949646503</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q98" t="b">
+        <v>0</v>
+      </c>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="n">
+        <v>400</v>
+      </c>
+      <c r="U98" s="1" t="n">
+        <v>33812</v>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>27/07/1992</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1228</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>46195.43472222222</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>GUILHERME HENRIQUE DA SILVA PONTOLLIO</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>086402581</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="n">
+        <v>52877627802</v>
+      </c>
+      <c r="N99" t="n">
+        <v>17</v>
+      </c>
+      <c r="O99" t="n">
+        <v>11987346138</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q99" t="b">
+        <v>0</v>
+      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="n">
+        <v>400</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15/04/2009 </t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>15/04/2009</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Equipe - Clínica Sallet</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1229</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>46195.65625</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>anônima</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>EVELYN GOMES SANTOS DE CASTRO LÉ</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>087952429</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="n">
+        <v>14582143709</v>
+      </c>
+      <c r="N100" t="n">
+        <v>36</v>
+      </c>
+      <c r="O100" t="n">
+        <v>21986129699</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="Q100" t="b">
+        <v>0</v>
+      </c>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="n">
+        <v>700</v>
+      </c>
+      <c r="U100" s="1" t="n">
+        <v>32948</v>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>16/03/1990</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Equipe - Cirurgião Michel Menezes</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>ENVIADO CAPTAÇÃO E NAVEGAÇÃO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
